--- a/Planejamento/Pinagem_Aquabox.xlsx
+++ b/Planejamento/Pinagem_Aquabox.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Repositorio_Git\Aquabox_Final\Planejamento\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB59831D-B1E1-4E03-A19E-650CAA011189}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C5B53D93-671D-4FEC-A4D7-B3EE7AFED792}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{C45012FE-CCAE-472D-B96D-BD2AAEEC4D20}"/>
   </bookViews>
@@ -60,9 +60,6 @@
     <t>Utilizado</t>
   </si>
   <si>
-    <t>DS3231M</t>
-  </si>
-  <si>
     <t>GPIO2</t>
   </si>
   <si>
@@ -270,27 +267,6 @@
     <t>GPIO48</t>
   </si>
   <si>
-    <t>Display SPI_DC</t>
-  </si>
-  <si>
-    <t>Display SPI_MOSI</t>
-  </si>
-  <si>
-    <t>Display SPI_SCK</t>
-  </si>
-  <si>
-    <t>Display SPI_RESET</t>
-  </si>
-  <si>
-    <t>Display SPI_Chip_Select</t>
-  </si>
-  <si>
-    <t>Display SD_CS</t>
-  </si>
-  <si>
-    <t>Sensor de fluxo</t>
-  </si>
-  <si>
     <t>Relé da bomba 220V AC</t>
   </si>
   <si>
@@ -337,6 +313,30 @@
   </si>
   <si>
     <t>FLASH/PSRAM</t>
+  </si>
+  <si>
+    <t>RTC - DS3231M</t>
+  </si>
+  <si>
+    <t>Display TFT 1.8" ST7735 -  SPI_DC</t>
+  </si>
+  <si>
+    <t>Display TFT 1.8" ST7735 -  SPI_Chip_Select</t>
+  </si>
+  <si>
+    <t>Display TFT 1.8" ST7735 -  SPI_RESET</t>
+  </si>
+  <si>
+    <t>Display TFT 1.8" ST7735 -  SPI_MOSI</t>
+  </si>
+  <si>
+    <t>Display TFT 1.8" ST7735 -  SPI_SCK</t>
+  </si>
+  <si>
+    <t>Display TFT 1.8" ST7735 -  SD_CS</t>
+  </si>
+  <si>
+    <t>Sensor de fluxo Hall</t>
   </si>
 </sst>
 </file>
@@ -754,7 +754,7 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>97</v>
+        <v>89</v>
       </c>
       <c r="B1" s="4"/>
       <c r="C1" s="4"/>
@@ -791,497 +791,497 @@
         <v>6</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>7</v>
+        <v>92</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B5" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="2" t="s">
-        <v>9</v>
-      </c>
       <c r="C5" s="2" t="s">
         <v>6</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>7</v>
+        <v>92</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B6" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D6" s="1" t="s">
         <v>14</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>15</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B7" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D7" s="2" t="s">
         <v>16</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B8" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D8" s="1" t="s">
         <v>18</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>19</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B9" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D9" s="2" t="s">
         <v>20</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>77</v>
+        <v>93</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>6</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>81</v>
+        <v>94</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>80</v>
+        <v>95</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>6</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>78</v>
+        <v>96</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>79</v>
+        <v>97</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>6</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>82</v>
+        <v>98</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B16" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="B16" s="1" t="s">
-        <v>35</v>
-      </c>
       <c r="C16" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>83</v>
+        <v>99</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="B17" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="B17" s="2" t="s">
-        <v>37</v>
-      </c>
       <c r="C17" s="2" t="s">
         <v>6</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>85</v>
+        <v>77</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>6</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>86</v>
+        <v>78</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>87</v>
+        <v>79</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C21" s="2" t="s">
         <v>6</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>89</v>
+        <v>81</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C22" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>88</v>
+        <v>80</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>6</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>90</v>
+        <v>82</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C24" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>91</v>
+        <v>83</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C25" s="2" t="s">
         <v>6</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C26" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="B27" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="B27" s="2" t="s">
-        <v>57</v>
-      </c>
       <c r="C27" s="2" t="s">
         <v>6</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="B28" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="B28" s="1" t="s">
-        <v>59</v>
-      </c>
       <c r="C28" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="B29" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="B29" s="2" t="s">
+      <c r="C29" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="C29" s="2" t="s">
-        <v>75</v>
-      </c>
       <c r="D29" s="2" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B30" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="C30" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="C30" s="1" t="s">
-        <v>75</v>
-      </c>
       <c r="D30" s="1" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B31" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C31" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="C31" s="2" t="s">
-        <v>70</v>
-      </c>
       <c r="D31" s="2" t="s">
-        <v>98</v>
+        <v>90</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B32" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="C32" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="C32" s="1" t="s">
-        <v>70</v>
-      </c>
       <c r="D32" s="1" t="s">
-        <v>98</v>
+        <v>90</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>98</v>
+        <v>90</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>98</v>
+        <v>90</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>99</v>
+        <v>91</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>98</v>
+        <v>90</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>99</v>
+        <v>91</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>98</v>
+        <v>90</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>99</v>
+        <v>91</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>98</v>
+        <v>90</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B38" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="C38" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="C38" s="1" t="s">
-        <v>70</v>
-      </c>
       <c r="D38" s="2" t="s">
-        <v>98</v>
+        <v>90</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="B39" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="B39" s="2" t="s">
+      <c r="C39" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="C39" s="2" t="s">
-        <v>70</v>
-      </c>
       <c r="D39" s="2" t="s">
-        <v>98</v>
+        <v>90</v>
       </c>
     </row>
   </sheetData>

--- a/Planejamento/Pinagem_Aquabox.xlsx
+++ b/Planejamento/Pinagem_Aquabox.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Repositorio_Git\Aquabox_Final\Planejamento\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C5B53D93-671D-4FEC-A4D7-B3EE7AFED792}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52BAD595-D97F-49F6-80D5-AF30783B33F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{C45012FE-CCAE-472D-B96D-BD2AAEEC4D20}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="100">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="245" uniqueCount="114">
   <si>
     <t>GPIO</t>
   </si>
@@ -337,6 +337,48 @@
   </si>
   <si>
     <t>Sensor de fluxo Hall</t>
+  </si>
+  <si>
+    <t>Ativo</t>
+  </si>
+  <si>
+    <t>Pull-up/pull-down</t>
+  </si>
+  <si>
+    <t>Isolamento</t>
+  </si>
+  <si>
+    <t>I2C</t>
+  </si>
+  <si>
+    <t>SPI</t>
+  </si>
+  <si>
+    <t>alto</t>
+  </si>
+  <si>
+    <t>pulsos</t>
+  </si>
+  <si>
+    <t>optoacoplado</t>
+  </si>
+  <si>
+    <t>direto</t>
+  </si>
+  <si>
+    <t>externo</t>
+  </si>
+  <si>
+    <t>direção</t>
+  </si>
+  <si>
+    <t>entrada</t>
+  </si>
+  <si>
+    <t>saída</t>
+  </si>
+  <si>
+    <t>baixo</t>
   </si>
 </sst>
 </file>
@@ -420,7 +462,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
@@ -430,6 +472,7 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -744,29 +787,39 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F1227E53-9378-4EA7-A254-0121DB46A913}">
-  <dimension ref="A1:D39"/>
+  <dimension ref="A1:H39"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="15.7109375" customWidth="1"/>
+    <col min="2" max="2" width="17" customWidth="1"/>
     <col min="3" max="3" width="17.28515625" customWidth="1"/>
-    <col min="4" max="4" width="38.140625" customWidth="1"/>
+    <col min="4" max="4" width="39.140625" customWidth="1"/>
+    <col min="6" max="6" width="17.7109375" customWidth="1"/>
+    <col min="7" max="7" width="13.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
         <v>89</v>
       </c>
       <c r="B1" s="4"/>
       <c r="C1" s="4"/>
       <c r="D1" s="4"/>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E1" s="4"/>
+      <c r="F1" s="4"/>
+      <c r="G1" s="4"/>
+      <c r="H1" s="4"/>
+    </row>
+    <row r="2" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="4"/>
       <c r="B2" s="4"/>
       <c r="C2" s="4"/>
       <c r="D2" s="4"/>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E2" s="4"/>
+      <c r="F2" s="4"/>
+      <c r="G2" s="4"/>
+      <c r="H2" s="4"/>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
         <v>0</v>
       </c>
@@ -779,8 +832,20 @@
       <c r="D3" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E3" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>4</v>
       </c>
@@ -793,8 +858,18 @@
       <c r="D4" s="1" t="s">
         <v>92</v>
       </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E4" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="H4" s="1"/>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>7</v>
       </c>
@@ -807,8 +882,18 @@
       <c r="D5" s="2" t="s">
         <v>92</v>
       </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E5" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="H5" s="1"/>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>9</v>
       </c>
@@ -821,8 +906,20 @@
       <c r="D6" s="1" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E6" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="H6" s="5" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>10</v>
       </c>
@@ -835,8 +932,20 @@
       <c r="D7" s="2" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E7" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="H7" s="5" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>11</v>
       </c>
@@ -849,8 +958,20 @@
       <c r="D8" s="1" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E8" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="H8" s="5" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>12</v>
       </c>
@@ -863,8 +984,20 @@
       <c r="D9" s="2" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E9" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="G9" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="H9" s="5" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>21</v>
       </c>
@@ -877,8 +1010,18 @@
       <c r="D10" s="1" t="s">
         <v>93</v>
       </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E10" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="G10" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="H10" s="1"/>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>22</v>
       </c>
@@ -891,8 +1034,18 @@
       <c r="D11" s="2" t="s">
         <v>94</v>
       </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E11" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="G11" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="H11" s="1"/>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
         <v>23</v>
       </c>
@@ -905,8 +1058,18 @@
       <c r="D12" s="1" t="s">
         <v>95</v>
       </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E12" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="G12" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="H12" s="1"/>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
         <v>24</v>
       </c>
@@ -919,8 +1082,18 @@
       <c r="D13" s="2" t="s">
         <v>96</v>
       </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E13" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="F13" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="G13" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="H13" s="1"/>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
         <v>25</v>
       </c>
@@ -933,8 +1106,18 @@
       <c r="D14" s="1" t="s">
         <v>97</v>
       </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E14" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="F14" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="G14" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="H14" s="1"/>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
         <v>26</v>
       </c>
@@ -947,8 +1130,18 @@
       <c r="D15" s="2" t="s">
         <v>98</v>
       </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E15" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="F15" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="G15" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="H15" s="1"/>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
         <v>33</v>
       </c>
@@ -961,8 +1154,20 @@
       <c r="D16" s="1" t="s">
         <v>99</v>
       </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E16" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="F16" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="G16" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="H16" s="5" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
         <v>35</v>
       </c>
@@ -975,8 +1180,20 @@
       <c r="D17" s="2" t="s">
         <v>76</v>
       </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E17" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="F17" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="G17" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="H17" s="5" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
         <v>37</v>
       </c>
@@ -989,8 +1206,20 @@
       <c r="D18" s="1" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E18" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="F18" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="G18" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="H18" s="5" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
         <v>38</v>
       </c>
@@ -1003,8 +1232,20 @@
       <c r="D19" s="2" t="s">
         <v>78</v>
       </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E19" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="F19" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="G19" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="H19" s="5" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
         <v>39</v>
       </c>
@@ -1017,8 +1258,20 @@
       <c r="D20" s="1" t="s">
         <v>79</v>
       </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E20" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="F20" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="G20" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="H20" s="5" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
         <v>43</v>
       </c>
@@ -1031,8 +1284,20 @@
       <c r="D21" s="2" t="s">
         <v>81</v>
       </c>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E21" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="F21" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="G21" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="H21" s="5" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
         <v>44</v>
       </c>
@@ -1045,8 +1310,20 @@
       <c r="D22" s="1" t="s">
         <v>80</v>
       </c>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E22" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="F22" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="G22" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="H22" s="5" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
         <v>45</v>
       </c>
@@ -1059,8 +1336,20 @@
       <c r="D23" s="2" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E23" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="F23" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="G23" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="H23" s="5" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
         <v>46</v>
       </c>
@@ -1073,8 +1362,20 @@
       <c r="D24" s="1" t="s">
         <v>83</v>
       </c>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E24" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="F24" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="G24" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="H24" s="5" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
         <v>47</v>
       </c>
@@ -1087,8 +1388,20 @@
       <c r="D25" s="2" t="s">
         <v>84</v>
       </c>
-    </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E25" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="F25" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="G25" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="H25" s="5" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
         <v>48</v>
       </c>
@@ -1101,8 +1414,20 @@
       <c r="D26" s="1" t="s">
         <v>85</v>
       </c>
-    </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E26" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="F26" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="G26" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="H26" s="5" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
         <v>55</v>
       </c>
@@ -1115,8 +1440,20 @@
       <c r="D27" s="2" t="s">
         <v>86</v>
       </c>
-    </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E27" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="F27" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="G27" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="H27" s="5" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
         <v>57</v>
       </c>
@@ -1129,8 +1466,20 @@
       <c r="D28" s="1" t="s">
         <v>87</v>
       </c>
-    </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E28" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="F28" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="G28" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="H28" s="5" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
         <v>72</v>
       </c>
@@ -1143,8 +1492,12 @@
       <c r="D29" s="2" t="s">
         <v>88</v>
       </c>
-    </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E29" s="1"/>
+      <c r="F29" s="1"/>
+      <c r="G29" s="1"/>
+      <c r="H29" s="1"/>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
         <v>75</v>
       </c>
@@ -1157,8 +1510,12 @@
       <c r="D30" s="1" t="s">
         <v>88</v>
       </c>
-    </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E30" s="1"/>
+      <c r="F30" s="1"/>
+      <c r="G30" s="1"/>
+      <c r="H30" s="1"/>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
         <v>61</v>
       </c>
@@ -1171,8 +1528,12 @@
       <c r="D31" s="2" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E31" s="1"/>
+      <c r="F31" s="1"/>
+      <c r="G31" s="1"/>
+      <c r="H31" s="1"/>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
         <v>62</v>
       </c>
@@ -1185,8 +1546,12 @@
       <c r="D32" s="1" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E32" s="1"/>
+      <c r="F32" s="1"/>
+      <c r="G32" s="1"/>
+      <c r="H32" s="1"/>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
         <v>59</v>
       </c>
@@ -1199,8 +1564,12 @@
       <c r="D33" s="2" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E33" s="1"/>
+      <c r="F33" s="1"/>
+      <c r="G33" s="1"/>
+      <c r="H33" s="1"/>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
         <v>60</v>
       </c>
@@ -1213,8 +1582,12 @@
       <c r="D34" s="2" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E34" s="1"/>
+      <c r="F34" s="1"/>
+      <c r="G34" s="1"/>
+      <c r="H34" s="1"/>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
         <v>63</v>
       </c>
@@ -1227,8 +1600,12 @@
       <c r="D35" s="2" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E35" s="1"/>
+      <c r="F35" s="1"/>
+      <c r="G35" s="1"/>
+      <c r="H35" s="1"/>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
         <v>64</v>
       </c>
@@ -1241,8 +1618,12 @@
       <c r="D36" s="2" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E36" s="1"/>
+      <c r="F36" s="1"/>
+      <c r="G36" s="1"/>
+      <c r="H36" s="1"/>
+    </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
         <v>65</v>
       </c>
@@ -1255,8 +1636,12 @@
       <c r="D37" s="2" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E37" s="1"/>
+      <c r="F37" s="1"/>
+      <c r="G37" s="1"/>
+      <c r="H37" s="1"/>
+    </row>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
         <v>66</v>
       </c>
@@ -1269,8 +1654,12 @@
       <c r="D38" s="2" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E38" s="1"/>
+      <c r="F38" s="1"/>
+      <c r="G38" s="1"/>
+      <c r="H38" s="1"/>
+    </row>
+    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
         <v>67</v>
       </c>
@@ -1283,10 +1672,14 @@
       <c r="D39" s="2" t="s">
         <v>90</v>
       </c>
+      <c r="E39" s="1"/>
+      <c r="F39" s="1"/>
+      <c r="G39" s="1"/>
+      <c r="H39" s="1"/>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:D2"/>
+    <mergeCell ref="A1:H2"/>
   </mergeCells>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
